--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487504_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487504_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8536</v>
+        <v>13.1352</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3698</v>
+        <v>12.8386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4838</v>
+        <v>0.2967</v>
       </c>
       <c r="G2" t="n">
         <v>12.5858</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2034</v>
+        <v>-0.9218</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1286</v>
+        <v>-0.6599</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0747</v>
+        <v>-0.2619</v>
       </c>
       <c r="V2" t="n">
         <v>0.8837</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.1681</v>
+        <v>10.0763</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8742</v>
+        <v>10.7289</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.706</v>
+        <v>-0.6526</v>
       </c>
       <c r="G3" t="n">
         <v>6.3237</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.409</v>
+        <v>-0.5008</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1494</v>
+        <v>-0.2947</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2596</v>
+        <v>-0.2061</v>
       </c>
       <c r="V3" t="n">
         <v>2.4908</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3928</v>
+        <v>6.9463</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2497</v>
+        <v>6.6161</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1431</v>
+        <v>0.3303</v>
       </c>
       <c r="G4" t="n">
         <v>9.0602</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7261</v>
+        <v>-1.1726</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9504</v>
+        <v>-0.584</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.5886</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9412</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5736</v>
+        <v>3.5469</v>
       </c>
       <c r="E5" t="n">
         <v>2.114</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4596</v>
+        <v>1.4329</v>
       </c>
       <c r="G5" t="n">
         <v>2.238</v>
@@ -844,13 +844,13 @@
         <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1125</v>
+        <v>-0.1392</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0063</v>
+        <v>-0.0204</v>
       </c>
       <c r="V5" t="n">
         <v>1.0564</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RUANO MARTINEZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.418</v>
+        <v>1.0114</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.985</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7028</v>
+        <v>0.0264</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3975</v>
+        <v>1.5963</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6608000000000001</v>
+        <v>1.7428</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7367</v>
+        <v>-0.1465</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8681</v>
+        <v>1.2391</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4235</v>
+        <v>0.9918</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4446</v>
+        <v>0.2473</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2656</v>
+        <v>0.3572</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0843</v>
+        <v>0.751</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1813</v>
+        <v>-0.3938</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5229</v>
+        <v>-0.268</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2952</v>
+        <v>-0.2541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2277</v>
+        <v>-0.014</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0576</v>
+        <v>-1.492</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4481</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3905</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>M. RUANO MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0427</v>
+        <v>0.5159</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8827</v>
+        <v>0.1606</v>
       </c>
       <c r="F7" t="n">
-        <v>0.16</v>
+        <v>0.3553</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5963</v>
+        <v>-1.3975</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7428</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1465</v>
+        <v>-0.7367</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2391</v>
+        <v>0.8681</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9918</v>
+        <v>0.4235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2473</v>
+        <v>0.4446</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3572</v>
+        <v>-2.2656</v>
       </c>
       <c r="N7" t="n">
-        <v>0.751</v>
+        <v>-1.0843</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3938</v>
+        <v>-1.1813</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2367</v>
+        <v>-0.3792</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3564</v>
+        <v>-0.2594</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1197</v>
+        <v>-0.1198</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.492</v>
+        <v>-0.0576</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.4481</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.492</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1333</v>
+        <v>0.3693</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2822</v>
+        <v>-0.1798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4154</v>
+        <v>0.5491</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2528</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2014</v>
+        <v>0.0346</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0362</v>
+        <v>0.1698</v>
       </c>
       <c r="V8" t="n">
         <v>0.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5531</v>
+        <v>-0.4462</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1359</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4172</v>
+        <v>-0.3103</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8379</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3028</v>
+        <v>-0.1958</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4575</v>
+        <v>-1.0331</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2381</v>
+        <v>-0.974</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2194</v>
+        <v>-0.059</v>
       </c>
       <c r="G10" t="n">
         <v>1.4063</v>
@@ -1234,13 +1234,13 @@
         <v>2.3502</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7439</v>
+        <v>-1.3195</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9504</v>
+        <v>-0.6864</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7935</v>
+        <v>-0.6331</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4908</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8594</v>
+        <v>-4.1129</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5687</v>
+        <v>-0.8757</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2907</v>
+        <v>-3.2372</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5571</v>
@@ -1312,13 +1312,13 @@
         <v>0.5875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5814</v>
+        <v>0.3279</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3258</v>
+        <v>0.0188</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2556</v>
+        <v>0.3091</v>
       </c>
       <c r="V11" t="n">
         <v>-1.492</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>29.7121</v>
+        <v>30.00910000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>30.9807</v>
+        <v>31.27780000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2686</v>
+        <v>-1.2684</v>
       </c>
       <c r="G12" t="n">
         <v>27.16500000000001</v>
@@ -1390,10 +1390,10 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.8315</v>
+        <v>-4.5344</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5082</v>
+        <v>-3.2114</v>
       </c>
       <c r="U12" t="n">
         <v>-1.3232</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0625</v>
+        <v>0.7764</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4003</v>
+        <v>4.2746</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3378</v>
+        <v>-3.4982</v>
       </c>
       <c r="G13" t="n">
         <v>0.3636</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3909</v>
+        <v>1.1048</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7962</v>
+        <v>0.6705</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5947</v>
+        <v>0.4343</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6712</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.422</v>
+        <v>-1.1104</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1983</v>
+        <v>0.403</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6203</v>
+        <v>-1.5134</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4329</v>
@@ -1546,13 +1546,13 @@
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.481</v>
+        <v>-0.1694</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="V14" t="n">
         <v>0.2754</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0672</v>
+        <v>-1.6236</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0865</v>
+        <v>0.6676</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.1537</v>
+        <v>-2.2911</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.485</v>
+        <v>-0.5431</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0003</v>
+        <v>-0.5179</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5154</v>
+        <v>-0.0252</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8795</v>
+        <v>2.6214</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0204</v>
+        <v>0.6362</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8591</v>
+        <v>1.9852</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3645</v>
+        <v>-3.1645</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0208</v>
+        <v>-1.1541</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3437</v>
+        <v>-2.0104</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2427</v>
+        <v>0.4121</v>
       </c>
       <c r="T15" t="n">
-        <v>0.207</v>
+        <v>0.0047</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0356</v>
+        <v>0.4074</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8249</v>
+        <v>-0.1217</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8249</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.362</v>
+        <v>-2.1161</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1511</v>
+        <v>1.9842</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2109</v>
+        <v>-4.1003</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5431</v>
+        <v>-0.485</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5179</v>
+        <v>-1.0003</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0252</v>
+        <v>0.5154</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6214</v>
+        <v>1.8795</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6362</v>
+        <v>0.0204</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9852</v>
+        <v>1.8591</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1645</v>
+        <v>-2.3645</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1541</v>
+        <v>-1.0208</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0104</v>
+        <v>-1.3437</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3264</v>
+        <v>0.1938</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.1047</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4876</v>
+        <v>0.0891</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1217</v>
+        <v>-1.8249</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1217</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.3468</v>
+        <v>-3.7817</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8359</v>
+        <v>-1.3242</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5109</v>
+        <v>-2.4575</v>
       </c>
       <c r="G17" t="n">
         <v>-3.0663</v>
@@ -1780,13 +1780,13 @@
         <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4396</v>
+        <v>0.1256</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7722</v>
+        <v>-0.2605</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3327</v>
+        <v>0.3861</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0576</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.4029</v>
+        <v>-4.0784</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6511</v>
+        <v>3.1628</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.0541</v>
+        <v>-7.2412</v>
       </c>
       <c r="G18" t="n">
         <v>-4.5071</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2846</v>
+        <v>0.6092</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3694</v>
+        <v>0.1423</v>
       </c>
       <c r="U18" t="n">
-        <v>0.654</v>
+        <v>0.4668</v>
       </c>
       <c r="V18" t="n">
         <v>0.2113</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.6101</v>
+        <v>-4.6776</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.507</v>
+        <v>-1.3501</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1031</v>
+        <v>-3.3275</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.5032</v>
+        <v>-3.8181</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4205</v>
+        <v>-2.3123</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.0827</v>
+        <v>-1.5057</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.8297</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4814</v>
+        <v>-0.4781</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2692</v>
+        <v>1.3077</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.7154</v>
+        <v>-4.6477</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9019</v>
+        <v>-1.8342</v>
       </c>
       <c r="O19" t="n">
         <v>-2.8135</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7626</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.4711</v>
       </c>
       <c r="T19" t="n">
-        <v>0.117</v>
+        <v>-0.0876</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5589</v>
+        <v>0.5587</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9798</v>
+        <v>1.6071</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1014</v>
+        <v>1.8249</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1217</v>
+        <v>-0.2178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7557</v>
+        <v>-5.7881</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2003</v>
+        <v>-2.7117</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5554</v>
+        <v>-3.0763</v>
       </c>
       <c r="G20" t="n">
-        <v>-9.172700000000001</v>
+        <v>-5.5032</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7805</v>
+        <v>-1.4205</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.3923</v>
+        <v>-4.0827</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.7741</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.461</v>
+        <v>0.4814</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.2351</v>
+        <v>-1.2692</v>
       </c>
       <c r="M20" t="n">
-        <v>-6.3987</v>
+        <v>-4.7154</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2415</v>
+        <v>-1.9019</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.1572</v>
+        <v>-2.8135</v>
       </c>
       <c r="P20" t="n">
         <v>-1.7626</v>
@@ -2014,28 +2014,28 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1435</v>
+        <v>0.498</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6854</v>
+        <v>-0.0876</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4581</v>
+        <v>0.5856</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0362</v>
+        <v>0.9798</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8260999999999999</v>
+        <v>1.1014</v>
       </c>
       <c r="X20" t="n">
-        <v>1.2101</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8079</v>
+        <v>-7.3129</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3734</v>
+        <v>-3.8377</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4344</v>
+        <v>-3.4752</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8181</v>
+        <v>-9.172700000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3123</v>
+        <v>-1.7805</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5057</v>
+        <v>-7.3923</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8297</v>
+        <v>-2.7741</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4781</v>
+        <v>0.461</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3077</v>
+        <v>-3.2351</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.6477</v>
+        <v>-6.3987</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8342</v>
+        <v>-2.2415</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.8135</v>
+        <v>-4.1572</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.7626</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-2.9377</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6592</v>
+        <v>1.5863</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.111</v>
+        <v>1.048</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4518</v>
+        <v>0.5383</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6071</v>
+        <v>2.0362</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8249</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2178</v>
+        <v>1.2101</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-29.7121</v>
+        <v>-29.7124</v>
       </c>
       <c r="E22" t="n">
-        <v>1.268499999999999</v>
+        <v>1.2685</v>
       </c>
       <c r="F22" t="n">
-        <v>-30.9806</v>
+        <v>-30.9807</v>
       </c>
       <c r="G22" t="n">
         <v>-27.1648</v>
@@ -2143,7 +2143,7 @@
         <v>-16.2698</v>
       </c>
       <c r="J22" t="n">
-        <v>9.2293</v>
+        <v>9.229299999999999</v>
       </c>
       <c r="K22" t="n">
         <v>3.3747</v>
@@ -2152,7 +2152,7 @@
         <v>5.8546</v>
       </c>
       <c r="M22" t="n">
-        <v>-36.3943</v>
+        <v>-36.39429999999999</v>
       </c>
       <c r="N22" t="n">
         <v>-14.2698</v>
@@ -2161,22 +2161,22 @@
         <v>-22.1245</v>
       </c>
       <c r="P22" t="n">
-        <v>-8.8131</v>
+        <v>-8.813100000000002</v>
       </c>
       <c r="Q22" t="n">
         <v>-14.6885</v>
       </c>
       <c r="R22" t="n">
-        <v>5.8752</v>
+        <v>5.875200000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>4.831399999999999</v>
+        <v>4.8315</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3232</v>
+        <v>1.3234</v>
       </c>
       <c r="U22" t="n">
-        <v>3.5082</v>
+        <v>3.5081</v>
       </c>
       <c r="V22" t="n">
         <v>1.434400000000001</v>
@@ -2185,7 +2185,7 @@
         <v>5.4046</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.9703</v>
+        <v>-3.970300000000001</v>
       </c>
     </row>
   </sheetData>
